--- a/reports/pdf_rolling5_20260811.xlsx
+++ b/reports/pdf_rolling5_20260811.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-04 ~ 2026-08-11  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-04 ~ 2026-08-11  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,326억   ·   현금 233억(5.3%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 11종목  /  매도 7종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,326억   ·   현금 265억(5.5%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 11종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -658,44 +658,44 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>2392896000</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.80%→1.38%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>72→116</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
           <t>덕산하이메탈</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>438738800</v>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>1.62%→1.67%</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>691→737</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>에스에이엠티</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
         <v>-46</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-474747600</v>
+        <v>-463376400</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.50%</t>
+          <t>1.62%→1.42%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>251→205</t>
+          <t>691→645</t>
         </is>
       </c>
     </row>
@@ -709,11 +709,11 @@
         <v>30</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1497105000</v>
+        <v>1680960000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>0.77%→1.15%</t>
+          <t>0.77%→1.18%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -723,111 +723,111 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에스에이엠티</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-19</v>
+        <v>-46</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1125275000</v>
+        <v>-526391800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>1.11%→0.78%</t>
+          <t>0.58%→0.51%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>74→55</t>
+          <t>251→205</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>에스피지  (신규)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1454463000</v>
+        <v>2544306000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.80%→1.27%</t>
+          <t>0.00%→0.55%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>72→99</t>
+          <t>0→23</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-14</v>
+        <v>-28</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-234613400</v>
+        <v>-914228000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.14%→0.10%</t>
+          <t>1.02%→0.80%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>40→26</t>
+          <t>140→112</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>에스피지  (신규)</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2409273000</v>
+        <v>7885680000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.57%</t>
+          <t>4.86%→6.25%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>0→23</t>
+          <t>58→80</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-9</v>
+        <v>-19</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1155042000</v>
+        <v>-1285749000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>7.05%→6.14%</t>
+          <t>1.11%→0.81%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>210→201</t>
+          <t>74→55</t>
         </is>
       </c>
     </row>
@@ -841,11 +841,11 @@
         <v>22</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>453200000</v>
+        <v>527978000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.14%</t>
+          <t>1.02%→1.22%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -855,67 +855,67 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-3508695000</v>
+        <v>-242256000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>4.03%→2.97%</t>
+          <t>0.14%→0.10%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>41→32</t>
+          <t>40→26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>17</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>5340550000</v>
+        <v>1535627000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>4.86%→5.61%</t>
+          <t>2.56%→3.27%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>58→75</t>
+          <t>149→166</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-407880000</v>
+        <v>-331402500</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.47%</t>
+          <t>0.31%→0.20%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>47→39</t>
+          <t>49→36</t>
         </is>
       </c>
     </row>
@@ -929,11 +929,11 @@
         <v>16</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>463088000</v>
+        <v>474624000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>3.52%→3.62%</t>
+          <t>3.52%→3.40%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -943,23 +943,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1915800000</v>
+        <v>-1789728000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.57%</t>
+          <t>0.84%→0.42%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>9→5</t>
+          <t>25→13</t>
         </is>
       </c>
     </row>
@@ -973,11 +973,11 @@
         <v>10</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>468650000</v>
+        <v>506760000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>1.19%→1.36%</t>
+          <t>1.19%→1.35%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -985,11 +985,27 @@
           <t>112→122</t>
         </is>
       </c>
-      <c r="G13" s="17" t="n"/>
-      <c r="H13" s="17" t="n"/>
-      <c r="I13" s="17" t="n"/>
-      <c r="J13" s="17" t="n"/>
-      <c r="K13" s="17" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>-3800700000</v>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>4.03%→2.95%</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>41→32</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -1001,11 +1017,11 @@
         <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>386456000</v>
+        <v>434763000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.97%→0.99%</t>
+          <t>0.97%→1.02%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -1013,11 +1029,27 @@
           <t>68→75</t>
         </is>
       </c>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="n"/>
-      <c r="I14" s="17" t="n"/>
-      <c r="J14" s="17" t="n"/>
-      <c r="K14" s="17" t="n"/>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>-1321902000</v>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>7.05%→6.44%</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>210→201</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -1029,11 +1061,11 @@
         <v>4</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>453200000</v>
+        <v>477508000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>4.92%→5.85%</t>
+          <t>4.92%→5.65%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -1041,11 +1073,27 @@
           <t>213→217</t>
         </is>
       </c>
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="17" t="n"/>
-      <c r="I15" s="17" t="n"/>
-      <c r="J15" s="17" t="n"/>
-      <c r="K15" s="17" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS  (편출)</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>-868599000</v>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>0.22%→0.00%</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>9→0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -1057,11 +1105,11 @@
         <v>3</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>365856000</v>
+        <v>410043000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>2.42%→2.21%</t>
+          <t>2.42%→2.26%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -1069,1173 +1117,2149 @@
           <t>73→76</t>
         </is>
       </c>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="17" t="n"/>
-      <c r="I16" s="17" t="n"/>
-      <c r="J16" s="17" t="n"/>
-      <c r="K16" s="17" t="n"/>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,897억   ·   현금 50억(1.3%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 1종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-409116000</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>0.56%→0.43%</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>47→39</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-2014680000</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>1.09%→0.55%</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>9→5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>-763230000</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>3.30%→3.05%</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>58→55</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,897억   ·   현금 21억(0.5%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 8종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>큐라클</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>654825600</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>1.29%→1.59%</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>986→1,092</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>-2089137600</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>5.40%→4.93%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>363→330</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>1300833600</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>1.85%→2.65%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>542→613</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-1167408000</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>8.43%→7.17%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>297→286</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>오스코텍</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>1264032000</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>3.14%→3.39%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>652→715</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-1506120000</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>5.98%→5.28%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>111→104</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>433197600</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>1.48%→1.89%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>1,066→1,127</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="17" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>2075673600</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>8.36%→9.30%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>755→797</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="17" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>8052000000</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>9.50%→10.07%</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>192→242</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="17" t="n"/>
-      <c r="J21" s="17" t="n"/>
-      <c r="K21" s="17" t="n"/>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
-      <c r="I23" s="19" t="n"/>
-      <c r="J23" s="19" t="n"/>
-      <c r="K23" s="19" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
-      <c r="G25" s="19" t="n"/>
-      <c r="H25" s="19" t="n"/>
-      <c r="I25" s="19" t="n"/>
-      <c r="J25" s="19" t="n"/>
-      <c r="K25" s="19" t="n"/>
-    </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 264억   ·   현금 14억(5.2%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 12종목  /  매도 10종목</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="8" t="n"/>
+      <c r="B28" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>6247296000</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>9.50%→9.80%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>192→226</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>2109993600</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>8.39%→9.28%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>511→540</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
-        <v>170</v>
+        <v>13</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>297160000</v>
+        <v>1210809600</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>5.53%→6.67%</t>
+          <t>1.93%→2.64%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>810→980</t>
-        </is>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>에이프로</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>-199</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>-45069520</v>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>0.38%→0.20%</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>427→228</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>심텍홀딩스</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>17198800</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>0.59%→0.66%</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>547→609</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>-184</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>-107397120</v>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>7.82%→7.37%</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>3,430→3,246</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>121805200</v>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>7.08%→7.53%</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>700→747</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>-139</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>-243500200</v>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>3.67%→2.71%</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>536→397</t>
-        </is>
-      </c>
+          <t>107→120</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,466억   ·   현금 66억(2.5%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 1종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>30515520</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>3.09%→3.20%</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>622→646</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>한선엔지니어링</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>-98</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>-92802080</v>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>2.00%→1.63%</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>540→442</t>
-        </is>
-      </c>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C34" s="11" t="n">
-        <v>33630000</v>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>2.68%→2.80%</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>306→321</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>오로스테크놀로지</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>-38</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>-39247920</v>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>0.25%→0.10%</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>63→25</t>
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>40527000</v>
+        <v>10657152000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.09%</t>
+          <t>3.92%→7.67%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>39→83</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-24</v>
+        <v>-34</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-44414400</v>
+        <v>-1599686400</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.09%</t>
+          <t>3.02%→2.07%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>37→13</t>
+          <t>149→115</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>오이솔루션</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" s="11" t="n">
-        <v>28249200</v>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>0.11%→0.22%</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>14→28</t>
-        </is>
-      </c>
+      <c r="A36" s="17" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-8</v>
+        <v>-23</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-32588800</v>
+        <v>-2124261600</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.74%</t>
+          <t>2.39%→1.30%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>55→47</t>
+          <t>60→37</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C37" s="11" t="n">
-        <v>53990400</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>2.67%→2.87%</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>76→82</t>
-        </is>
-      </c>
+      <c r="A37" s="17" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-58520000</v>
+        <v>-1426800000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2.58%→2.34%</t>
+          <t>2.12%→1.42%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>79→72</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>26037600</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>0.90%→1.00%</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>53→59</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>-17920800</v>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>0.92%→0.85%</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>79→73</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>40264800</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>2.33%→2.48%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>89→95</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>-7843200</v>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>1.27%→1.23%</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>124→121</t>
-        </is>
-      </c>
+          <t>18→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,281억   ·   현금 25억(1.0%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 6종목  /  매도 6종목</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>42864000</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>2.68%→2.84%</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>96→102</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="n"/>
-      <c r="H40" s="17" t="n"/>
-      <c r="I40" s="17" t="n"/>
-      <c r="J40" s="17" t="n"/>
-      <c r="K40" s="17" t="n"/>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>4907884800</v>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>5.92%→8.27%</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>329→435</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>일동제약</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>-184</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>-982383360</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>0.96%→0.47%</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>400→216</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>2466072000</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>0.82%→1.97%</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>99→204</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>-160</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>-1231104000</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>0.73%→0.13%</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>202→42</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>97</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>1380271200</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>1.56%→2.31%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>299→396</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>HK이노엔  (편출)</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>-1244073600</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>0.63%→0.00%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>102→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="B41" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>92720000</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>1.27%→1.62%</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>14→18</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="n"/>
-      <c r="H41" s="17" t="n"/>
-      <c r="I41" s="17" t="n"/>
-      <c r="J41" s="17" t="n"/>
-      <c r="K41" s="17" t="n"/>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 33억(5.8%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 9종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K45" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="B45" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>11108160000</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>14.14%→17.09%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>261→356</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>-72</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>-4862592000</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>11.54%→8.29%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>371→299</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>363860000</v>
+        <v>3585489600</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.40%→3.36%</t>
+          <t>4.88%→6.43%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>446→559</t>
+          <t>300→389</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>펩트론  (편출)</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-43</v>
+        <v>-40</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-284337500</v>
+        <v>-2232384000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>6.77%→5.49%</t>
+          <t>1.13%→0.00%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>488→445</t>
+          <t>40→0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>오름테라퓨틱  (신규)</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>733205500</v>
+        <v>2430086400</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.37%</t>
+          <t>1.18%→2.46%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>0→103</t>
+          <t>60→101</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-33</v>
+        <v>-8</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1436407500</v>
+        <v>-4217472000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>7.47%→3.98%</t>
+          <t>7.77%→5.19%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>82→49</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>오스코텍</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="C48" s="11" t="n">
-        <v>120577500</v>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>3.59%→3.79%</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>475→505</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>-183356000</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>8.56%→7.87%</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>192→184</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>에이비엘바이오</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>298770000</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>7.18%→8.23%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>413→443</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="n"/>
-      <c r="H49" s="17" t="n"/>
-      <c r="I49" s="17" t="n"/>
-      <c r="J49" s="17" t="n"/>
-      <c r="K49" s="17" t="n"/>
+          <t>32→24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 264억   ·   현금 14억(5.0%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 14종목  /  매도 13종목</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>806725000</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>9.87%→9.81%</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>127→150</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="n"/>
-      <c r="H50" s="17" t="n"/>
-      <c r="I50" s="17" t="n"/>
-      <c r="J50" s="17" t="n"/>
-      <c r="K50" s="17" t="n"/>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>리가켐바이오</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>273378000</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>7.87%→8.69%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>337→358</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="n"/>
-      <c r="H51" s="17" t="n"/>
-      <c r="I51" s="17" t="n"/>
-      <c r="J51" s="17" t="n"/>
-      <c r="K51" s="17" t="n"/>
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>241741500</v>
+        <v>367080000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>5.43%→5.50%</t>
+          <t>5.53%→6.93%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>235→256</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="n"/>
-      <c r="H52" s="17" t="n"/>
-      <c r="I52" s="17" t="n"/>
-      <c r="J52" s="17" t="n"/>
-      <c r="K52" s="17" t="n"/>
+          <t>810→1,020</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>에이프로</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-199</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-45069520</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>0.38%→0.20%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>427→228</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>심텍홀딩스</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>223008000</v>
+        <v>17198800</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>8.38%→8.87%</t>
+          <t>0.59%→0.66%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>325→341</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="n"/>
-      <c r="I53" s="17" t="n"/>
-      <c r="J53" s="17" t="n"/>
-      <c r="K53" s="17" t="n"/>
+          <t>547→609</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-184</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-107397120</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>7.82%→7.37%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>3,430→3,246</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>121805200</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>7.08%→7.53%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>700→747</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-139</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-243500200</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>3.67%→2.70%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>536→397</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>30515520</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>3.09%→3.19%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>622→646</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-92802080</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>2.00%→1.63%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>540→442</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>27203440</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.11%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>0→22</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>금양그린파워</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-31539240</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>0.87%→0.75%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>375→322</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티  (신규)</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>11149960</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.04%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>0→17</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>오로스테크놀로지</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-38</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-39247920</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>0.25%→0.10%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>63→25</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>33630000</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>2.68%→2.80%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>306→321</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>상아프론테크</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-29908280</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>0.43%→0.31%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>107→78</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>40527000</v>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>0.94%→1.09%</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>89→104</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-32503680</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>1.64%→1.51%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>349→322</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>28249200</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>0.11%→0.22%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>14→28</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>네패스아크</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-44414400</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>0.27%→0.09%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>37→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>42864000</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>2.68%→2.83%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>96→102</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>하나머티리얼즈</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-32588800</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>0.87%→0.74%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>55→47</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>40264800</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>2.33%→2.48%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>89→95</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-58520000</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>2.58%→2.34%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>79→72</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>26037600</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>0.90%→1.00%</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>53→59</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-17920800</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>0.92%→0.85%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>79→73</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>53990400</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>2.67%→2.87%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>76→82</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-7843200</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>1.27%→1.23%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>124→121</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>92720000</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>1.27%→1.62%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>14→18</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="n"/>
+      <c r="H65" s="17" t="n"/>
+      <c r="I65" s="17" t="n"/>
+      <c r="J65" s="17" t="n"/>
+      <c r="K65" s="17" t="n"/>
+    </row>
+    <row r="67" ht="19" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 19억(3.1%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 10종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱  (신규)</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>179</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>1438891500</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.44%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>0→179</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-324886500</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>6.77%→5.69%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>488→445</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>168</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>670404000</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>2.40%→4.15%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>446→614</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-1555950000</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>7.47%→3.91%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>82→49</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>551655000</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>2.39%→3.58%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>368→498</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
           <t>휴젤</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C54" s="11" t="n">
-        <v>94357500</v>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>5.21%→5.40%</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>89→92</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="n"/>
-      <c r="H54" s="17" t="n"/>
-      <c r="I54" s="17" t="n"/>
-      <c r="J54" s="17" t="n"/>
-      <c r="K54" s="17" t="n"/>
-    </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="H72" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-707135000</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>5.21%→3.65%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>89→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>오스코텍</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>131100000</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>3.59%→3.74%</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>475→505</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>-184920000</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>8.56%→7.20%</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>192→184</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>322920000</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>7.18%→8.07%</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>413→443</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="n"/>
+      <c r="H74" s="17" t="n"/>
+      <c r="I74" s="17" t="n"/>
+      <c r="J74" s="17" t="n"/>
+      <c r="K74" s="17" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>547722000</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>1.76%→3.06%</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>62→89</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="n"/>
+      <c r="H75" s="17" t="n"/>
+      <c r="I75" s="17" t="n"/>
+      <c r="J75" s="17" t="n"/>
+      <c r="K75" s="17" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>260820000</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>5.43%→5.38%</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>235→256</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="n"/>
+      <c r="H76" s="17" t="n"/>
+      <c r="I76" s="17" t="n"/>
+      <c r="J76" s="17" t="n"/>
+      <c r="K76" s="17" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>289558500</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>7.87%→8.36%</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>337→358</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="n"/>
+      <c r="H77" s="17" t="n"/>
+      <c r="I77" s="17" t="n"/>
+      <c r="J77" s="17" t="n"/>
+      <c r="K77" s="17" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>253552000</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>8.38%→9.15%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>325→341</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="n"/>
+      <c r="H78" s="17" t="n"/>
+      <c r="I78" s="17" t="n"/>
+      <c r="J78" s="17" t="n"/>
+      <c r="K78" s="17" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>480240000</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>9.87%→9.42%</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>127→139</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="n"/>
+      <c r="H79" s="17" t="n"/>
+      <c r="I79" s="17" t="n"/>
+      <c r="J79" s="17" t="n"/>
+      <c r="K79" s="17" t="n"/>
+    </row>
+    <row r="81" ht="19" customHeight="1">
+      <c r="A81" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B56" s="19" t="n"/>
-      <c r="C56" s="19" t="n"/>
-      <c r="D56" s="19" t="n"/>
-      <c r="E56" s="19" t="n"/>
-      <c r="F56" s="19" t="n"/>
-      <c r="G56" s="19" t="n"/>
-      <c r="H56" s="19" t="n"/>
-      <c r="I56" s="19" t="n"/>
-      <c r="J56" s="19" t="n"/>
-      <c r="K56" s="19" t="n"/>
+      <c r="B81" s="19" t="n"/>
+      <c r="C81" s="19" t="n"/>
+      <c r="D81" s="19" t="n"/>
+      <c r="E81" s="19" t="n"/>
+      <c r="F81" s="19" t="n"/>
+      <c r="G81" s="19" t="n"/>
+      <c r="H81" s="19" t="n"/>
+      <c r="I81" s="19" t="n"/>
+      <c r="J81" s="19" t="n"/>
+      <c r="K81" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="21">
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="G68:K68"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G28:K28"/>
-    <mergeCell ref="G44:K44"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="G50:K50"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260811.xlsx
+++ b/reports/pdf_rolling5_20260811.xlsx
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-3800700000</v>
+        <v>-1321902000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>4.03%→2.95%</t>
+          <t>7.05%→6.44%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>41→32</t>
+          <t>210→201</t>
         </is>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1321902000</v>
+        <v>-3800700000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>7.05%→6.44%</t>
+          <t>4.03%→2.95%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>210→201</t>
+          <t>41→32</t>
         </is>
       </c>
     </row>
@@ -2630,23 +2630,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>40264800</v>
+        <v>26037600</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.33%→2.48%</t>
+          <t>0.90%→1.00%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -2674,23 +2674,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>26037600</v>
+        <v>53990400</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>0.90%→1.00%</t>
+          <t>2.67%→2.87%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -2718,23 +2718,23 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>53990400</v>
+        <v>40264800</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.87%</t>
+          <t>2.33%→2.48%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -3111,23 +3111,23 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>260820000</v>
+        <v>289558500</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>5.43%→5.38%</t>
+          <t>7.87%→8.36%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>235→256</t>
+          <t>337→358</t>
         </is>
       </c>
       <c r="G76" s="17" t="n"/>
@@ -3139,23 +3139,23 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B77" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>289558500</v>
+        <v>260820000</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>7.87%→8.36%</t>
+          <t>5.43%→5.38%</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>337→358</t>
+          <t>235→256</t>
         </is>
       </c>
       <c r="G77" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260811.xlsx
+++ b/reports/pdf_rolling5_20260811.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,326억   ·   현금 265억(5.5%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 11종목  /  매도 13종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,738억   ·   현금 265억(5.5%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 11종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>44</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2392896000</v>
+        <v>2397542400</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-46</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-463376400</v>
+        <v>-464276160</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1680960000</v>
+        <v>1684224000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-46</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-526391800</v>
+        <v>-527413920</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>23</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2544306000</v>
+        <v>2549246400</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-28</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-914228000</v>
+        <v>-916003200</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>22</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>7885680000</v>
+        <v>7900992000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-19</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1285749000</v>
+        <v>-1288245600</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>527978000</v>
+        <v>529003200</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-14</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-242256000</v>
+        <v>-242726400</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1535627000</v>
+        <v>1538608800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-13</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-331402500</v>
+        <v>-332046000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>474624000</v>
+        <v>475545600</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1789728000</v>
+        <v>-1793203200</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>506760000</v>
+        <v>507744000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1321902000</v>
+        <v>-3808080000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>7.05%→6.44%</t>
+          <t>4.03%→2.95%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>210→201</t>
+          <t>41→32</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>434763000</v>
+        <v>435607200</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>원익IPS  (편출)</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-3800700000</v>
+        <v>-870285600</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>4.03%→2.95%</t>
+          <t>0.22%→0.00%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>41→32</t>
+          <t>9→0</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>477508000</v>
+        <v>478435200</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>원익IPS  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-868599000</v>
+        <v>-1324468800</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.22%→0.00%</t>
+          <t>7.05%→6.44%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>210→201</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>410043000</v>
+        <v>410839200</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-8</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-409116000</v>
+        <v>-409910400</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>-4</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-2014680000</v>
+        <v>-2018592000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>-3</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-763230000</v>
+        <v>-764712000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,897억   ·   현금 21억(0.5%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 8종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,270억   ·   현금 21억(0.5%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 8종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1559,7 +1559,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,466억   ·   현금 66억(2.5%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 1종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,676억   ·   현금 67억(2.5%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 1종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1655,7 +1655,7 @@
         <v>44</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>10657152000</v>
+        <v>10779648000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>-34</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1599686400</v>
+        <v>-1618073600</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>-23</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-2124261600</v>
+        <v>-2148678400</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>-5</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1426800000</v>
+        <v>-1443200000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,281억   ·   현금 25억(1.0%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 6종목  /  매도 6종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,463억   ·   현금 25억(1.0%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -1844,7 +1844,7 @@
         <v>106</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>4907884800</v>
+        <v>4922491600</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>-184</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-982383360</v>
+        <v>-985307120</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>105</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2466072000</v>
+        <v>2473411500</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>-160</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-1231104000</v>
+        <v>-1234768000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>97</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1380271200</v>
+        <v>1384379150</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>-102</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-1244073600</v>
+        <v>-1247776200</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>95</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>11108160000</v>
+        <v>11141220000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>-72</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-4862592000</v>
+        <v>-4877064000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>89</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>3585489600</v>
+        <v>3596160700</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>-40</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-2232384000</v>
+        <v>-2239028000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>41</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2430086400</v>
+        <v>2437318800</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>-8</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-4217472000</v>
+        <v>-4230024000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 264억   ·   현금 14억(5.0%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 14종목  /  매도 13종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 287억   ·   현금 14억(4.6%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 14종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B49" s="4" t="n"/>
@@ -2197,11 +2197,11 @@
         <v>210</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>367080000</v>
+        <v>395010000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>5.53%→6.93%</t>
+          <t>5.46%→6.84%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2218,11 +2218,11 @@
         <v>-199</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-45069520</v>
+        <v>-50892260</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.20%</t>
+          <t>0.39%→0.21%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2241,11 +2241,11 @@
         <v>62</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>17198800</v>
+        <v>20732800</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.59%→0.66%</t>
+          <t>0.66%→0.73%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2262,11 +2262,11 @@
         <v>-184</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-107397120</v>
+        <v>-118304640</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>7.82%→7.37%</t>
+          <t>7.90%→7.44%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2285,11 +2285,11 @@
         <v>47</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>121805200</v>
+        <v>133771400</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>7.08%→7.53%</t>
+          <t>7.14%→7.58%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2306,11 +2306,11 @@
         <v>-139</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-243500200</v>
+        <v>-265156400</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.67%→2.70%</t>
+          <t>3.66%→2.70%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2329,11 +2329,11 @@
         <v>24</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>30515520</v>
+        <v>32102400</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>3.09%→3.19%</t>
+          <t>2.98%→3.08%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2350,11 +2350,11 @@
         <v>-98</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-92802080</v>
+        <v>-100101120</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2.00%→1.63%</t>
+          <t>1.98%→1.61%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2373,11 +2373,11 @@
         <v>22</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>27203440</v>
+        <v>28089600</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.11%</t>
+          <t>0.00%→0.10%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2394,11 +2394,11 @@
         <v>-53</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-31539240</v>
+        <v>-32425400</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.75%</t>
+          <t>0.82%→0.70%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2417,11 +2417,11 @@
         <v>17</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>11149960</v>
+        <v>13824400</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.05%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2438,7 +2438,7 @@
         <v>-38</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-39247920</v>
+        <v>-41962640</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2454,23 +2454,23 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>33630000</v>
+        <v>46968000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.80%</t>
+          <t>1.00%→1.16%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>306→321</t>
+          <t>89→104</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2482,11 +2482,11 @@
         <v>-29</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-29908280</v>
+        <v>-31869840</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.43%→0.31%</t>
+          <t>0.42%→0.31%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2498,23 +2498,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>40527000</v>
+        <v>34656000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.09%</t>
+          <t>2.53%→2.65%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>306→321</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2526,11 +2526,11 @@
         <v>-27</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-32503680</v>
+        <v>-36689760</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.64%→1.51%</t>
+          <t>1.70%→1.56%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2549,11 +2549,11 @@
         <v>14</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>28249200</v>
+        <v>29579200</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.11%→0.22%</t>
+          <t>0.11%→0.21%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2570,7 +2570,7 @@
         <v>-24</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-44414400</v>
+        <v>-48700800</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2586,23 +2586,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>42864000</v>
+        <v>60511200</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.83%</t>
+          <t>2.75%→2.95%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -2614,11 +2614,11 @@
         <v>-8</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-32588800</v>
+        <v>-36662400</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.74%</t>
+          <t>0.90%→0.77%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2637,11 +2637,11 @@
         <v>6</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>26037600</v>
+        <v>27998400</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>0.90%→1.00%</t>
+          <t>0.89%→0.98%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2658,11 +2658,11 @@
         <v>-7</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-58520000</v>
+        <v>-61658800</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>2.58%→2.34%</t>
+          <t>2.49%→2.26%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2674,23 +2674,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>53990400</v>
+        <v>47880000</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.87%</t>
+          <t>2.74%→2.90%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -2702,11 +2702,11 @@
         <v>-6</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-17920800</v>
+        <v>-17510400</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.85%</t>
+          <t>0.83%→0.76%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2725,11 +2725,11 @@
         <v>6</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>40264800</v>
+        <v>44870400</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.33%→2.48%</t>
+          <t>2.38%→2.53%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2746,11 +2746,11 @@
         <v>-3</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-7843200</v>
+        <v>-8424600</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.23%</t>
+          <t>1.25%→1.21%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2769,11 +2769,11 @@
         <v>4</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>92720000</v>
+        <v>105792000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.62%</t>
+          <t>1.33%→1.70%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2790,7 +2790,7 @@
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 19억(3.1%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 10종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 621억   ·   현금 19억(3.1%)      오늘 2026-08-11  vs  5일전 2026-08-04      매수 10종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B67" s="4" t="n"/>
@@ -2886,7 +2886,7 @@
         <v>179</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>1438891500</v>
+        <v>1451403600</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>-43</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-324886500</v>
+        <v>-327711600</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>168</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>670404000</v>
+        <v>676233600</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>-33</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-1555950000</v>
+        <v>-1569480000</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>130</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>551655000</v>
+        <v>556452000</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>-22</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-707135000</v>
+        <v>-713284000</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
@@ -3011,23 +3011,23 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B73" s="11" t="n">
         <v>30</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>131100000</v>
+        <v>325728000</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>3.59%→3.74%</t>
+          <t>7.18%→8.07%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>475→505</t>
+          <t>413→443</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -3039,7 +3039,7 @@
         <v>-8</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-184920000</v>
+        <v>-186528000</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
@@ -3055,23 +3055,23 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
         <v>30</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>322920000</v>
+        <v>132240000</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>7.18%→8.07%</t>
+          <t>3.59%→3.74%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>413→443</t>
+          <t>475→505</t>
         </is>
       </c>
       <c r="G74" s="17" t="n"/>
@@ -3090,7 +3090,7 @@
         <v>27</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>547722000</v>
+        <v>552484800</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
@@ -3111,23 +3111,23 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>289558500</v>
+        <v>263088000</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>7.87%→8.36%</t>
+          <t>5.43%→5.38%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>337→358</t>
+          <t>235→256</t>
         </is>
       </c>
       <c r="G76" s="17" t="n"/>
@@ -3139,23 +3139,23 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B77" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>260820000</v>
+        <v>292076400</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>5.43%→5.38%</t>
+          <t>7.87%→8.36%</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>235→256</t>
+          <t>337→358</t>
         </is>
       </c>
       <c r="G77" s="17" t="n"/>
@@ -3174,7 +3174,7 @@
         <v>16</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>253552000</v>
+        <v>255756800</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>12</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>480240000</v>
+        <v>484416000</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260811.xlsx
+++ b/reports/pdf_rolling5_20260811.xlsx
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>원익IPS  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-870285600</v>
+        <v>-1324468800</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.22%→0.00%</t>
+          <t>7.05%→6.44%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>210→201</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>원익IPS  (편출)</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1324468800</v>
+        <v>-870285600</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>7.05%→6.44%</t>
+          <t>0.22%→0.00%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>210→201</t>
+          <t>9→0</t>
         </is>
       </c>
     </row>
@@ -2586,23 +2586,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>60511200</v>
+        <v>47880000</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.75%→2.95%</t>
+          <t>2.74%→2.90%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -2630,23 +2630,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>27998400</v>
+        <v>60511200</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>0.89%→0.98%</t>
+          <t>2.75%→2.95%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -2674,23 +2674,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>47880000</v>
+        <v>27998400</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>2.74%→2.90%</t>
+          <t>0.89%→0.98%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260811.xlsx
+++ b/reports/pdf_rolling5_20260811.xlsx
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-3808080000</v>
+        <v>-1324468800</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>4.03%→2.95%</t>
+          <t>7.05%→6.44%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>41→32</t>
+          <t>210→201</t>
         </is>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1324468800</v>
+        <v>-3808080000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>7.05%→6.44%</t>
+          <t>4.03%→2.95%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>210→201</t>
+          <t>41→32</t>
         </is>
       </c>
     </row>
@@ -2586,23 +2586,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>47880000</v>
+        <v>60511200</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.74%→2.90%</t>
+          <t>2.75%→2.95%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -2630,23 +2630,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>60511200</v>
+        <v>47880000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.75%→2.95%</t>
+          <t>2.74%→2.90%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -3111,23 +3111,23 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>263088000</v>
+        <v>292076400</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>5.43%→5.38%</t>
+          <t>7.87%→8.36%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>235→256</t>
+          <t>337→358</t>
         </is>
       </c>
       <c r="G76" s="17" t="n"/>
@@ -3139,23 +3139,23 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B77" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>292076400</v>
+        <v>263088000</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>7.87%→8.36%</t>
+          <t>5.43%→5.38%</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>337→358</t>
+          <t>235→256</t>
         </is>
       </c>
       <c r="G77" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260811.xlsx
+++ b/reports/pdf_rolling5_20260811.xlsx
@@ -679,23 +679,23 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>에스에이엠티</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
         <v>-46</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-464276160</v>
+        <v>-527413920</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.62%→1.42%</t>
+          <t>0.58%→0.51%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>691→645</t>
+          <t>251→205</t>
         </is>
       </c>
     </row>
@@ -723,23 +723,23 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>에스에이엠티</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-46</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-527413920</v>
+        <v>-464276160</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.51%</t>
+          <t>1.62%→1.42%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>251→205</t>
+          <t>691→645</t>
         </is>
       </c>
     </row>
@@ -790,23 +790,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>7900992000</v>
+        <v>529003200</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>4.86%→6.25%</t>
+          <t>1.02%→1.22%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>58→80</t>
+          <t>211→233</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -834,23 +834,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>529003200</v>
+        <v>7900992000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.22%</t>
+          <t>4.86%→6.25%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>211→233</t>
+          <t>58→80</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>원익IPS  (편출)</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1324468800</v>
+        <v>-870285600</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>7.05%→6.44%</t>
+          <t>0.22%→0.00%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>210→201</t>
+          <t>9→0</t>
         </is>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-3808080000</v>
+        <v>-1324468800</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>4.03%→2.95%</t>
+          <t>7.05%→6.44%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>41→32</t>
+          <t>210→201</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>원익IPS  (편출)</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-870285600</v>
+        <v>-3808080000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.22%→0.00%</t>
+          <t>4.03%→2.95%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>41→32</t>
         </is>
       </c>
     </row>
@@ -2630,23 +2630,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>47880000</v>
+        <v>44870400</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.74%→2.90%</t>
+          <t>2.38%→2.53%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -2674,23 +2674,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>27998400</v>
+        <v>47880000</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>0.89%→0.98%</t>
+          <t>2.74%→2.90%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -2718,23 +2718,23 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>44870400</v>
+        <v>27998400</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.53%</t>
+          <t>0.89%→0.98%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
